--- a/portfolio-lab/dist/examples/portfolio-m2-90-67.xlsx
+++ b/portfolio-lab/dist/examples/portfolio-m2-90-67.xlsx
@@ -418,7 +418,7 @@
     <col min="7" max="7" width="20.83203125" customWidth="1"/>
     <col min="8" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" customWidth="1"/>
   </cols>
@@ -452,7 +452,7 @@
         <v>ОФЗ / RGBITR</v>
       </c>
       <c r="J1" t="str">
-        <v>Нефть Brent</v>
+        <v>Индекс недвижимости</v>
       </c>
       <c r="K1" t="str">
         <v>Серебро</v>
@@ -490,7 +490,7 @@
         <v>100</v>
       </c>
       <c r="J2" s="1">
-        <v>4200</v>
+        <v>100</v>
       </c>
       <c r="K2" s="1">
         <v>38</v>
@@ -528,7 +528,7 @@
         <v>102.711122461</v>
       </c>
       <c r="J3" s="1">
-        <v>4526.69163103</v>
+        <v>103.440216982</v>
       </c>
       <c r="K3" s="1">
         <v>40.825862083</v>
@@ -566,7 +566,7 @@
         <v>107.027603882</v>
       </c>
       <c r="J4" s="1">
-        <v>5082.176549225</v>
+        <v>108.857791826</v>
       </c>
       <c r="K4" s="1">
         <v>45.381881173</v>
@@ -604,7 +604,7 @@
         <v>112.109749619</v>
       </c>
       <c r="J5" s="1">
-        <v>5733.195092569</v>
+        <v>114.793592768</v>
       </c>
       <c r="K5" s="1">
         <v>50.0907561</v>
@@ -642,7 +642,7 @@
         <v>116.821212601</v>
       </c>
       <c r="J6" s="1">
-        <v>6261.037235208</v>
+        <v>119.398625572</v>
       </c>
       <c r="K6" s="1">
         <v>52.809571628</v>
@@ -680,7 +680,7 @@
         <v>119.988378734</v>
       </c>
       <c r="J7" s="1">
-        <v>6430.978689497</v>
+        <v>121.087610002</v>
       </c>
       <c r="K7" s="1">
         <v>52.003581868</v>
@@ -718,7 +718,7 @@
         <v>120.796861646</v>
       </c>
       <c r="J8" s="1">
-        <v>6147.284043168</v>
+        <v>119.349176667</v>
       </c>
       <c r="K8" s="1">
         <v>48.12848554</v>
@@ -756,7 +756,7 @@
         <v>119.149771753</v>
       </c>
       <c r="J9" s="1">
-        <v>5551.375866946</v>
+        <v>115.113868459</v>
       </c>
       <c r="K9" s="1">
         <v>43.429755439</v>
@@ -794,7 +794,7 @@
         <v>115.748113392</v>
       </c>
       <c r="J10" s="1">
-        <v>4924.216941801</v>
+        <v>110.290509945</v>
       </c>
       <c r="K10" s="1">
         <v>40.193545936</v>
@@ -832,7 +832,7 @@
         <v>111.811703073</v>
       </c>
       <c r="J11" s="1">
-        <v>4497.550072568</v>
+        <v>106.830699273</v>
       </c>
       <c r="K11" s="1">
         <v>39.580104368</v>
@@ -870,7 +870,7 @@
         <v>108.619542408</v>
       </c>
       <c r="J12" s="1">
-        <v>4375.635959516</v>
+        <v>106.023696754</v>
       </c>
       <c r="K12" s="1">
         <v>41.728424951</v>
@@ -908,7 +908,7 @@
         <v>107.138492751</v>
       </c>
       <c r="J13" s="1">
-        <v>4572.34066924</v>
+        <v>108.27887357</v>
       </c>
       <c r="K13" s="1">
         <v>46.058213159</v>
@@ -946,7 +946,7 @@
         <v>107.860393001</v>
       </c>
       <c r="J14" s="1">
-        <v>5050.124674883</v>
+        <v>113.160782733</v>
       </c>
       <c r="K14" s="1">
         <v>51.198143774</v>
@@ -984,7 +984,7 @@
         <v>110.784620342</v>
       </c>
       <c r="J15" s="1">
-        <v>5710.788855684</v>
+        <v>119.454471488</v>
       </c>
       <c r="K15" s="1">
         <v>55.005483069</v>
@@ -1022,7 +1022,7 @@
         <v>115.440394166</v>
       </c>
       <c r="J16" s="1">
-        <v>6366.308648924</v>
+        <v>125.332009446</v>
       </c>
       <c r="K16" s="1">
         <v>55.462679628</v>
@@ -1060,7 +1060,7 @@
         <v>120.922016531</v>
       </c>
       <c r="J17" s="1">
-        <v>6760.774799102</v>
+        <v>128.850491104</v>
       </c>
       <c r="K17" s="1">
         <v>52.260202415</v>
@@ -1098,7 +1098,7 @@
         <v>126.003819019</v>
       </c>
       <c r="J18" s="1">
-        <v>6697.933797361</v>
+        <v>128.795176208</v>
       </c>
       <c r="K18" s="1">
         <v>47.29690862</v>
@@ -1136,7 +1136,7 @@
         <v>129.419936858</v>
       </c>
       <c r="J19" s="1">
-        <v>6200.813479693</v>
+        <v>125.395073813</v>
       </c>
       <c r="K19" s="1">
         <v>43.175576598</v>
@@ -1174,7 +1174,7 @@
         <v>130.291969704</v>
       </c>
       <c r="J20" s="1">
-        <v>5517.169991001</v>
+        <v>120.277504715</v>
       </c>
       <c r="K20" s="1">
         <v>41.54983836</v>
@@ -1212,7 +1212,7 @@
         <v>128.515412072</v>
       </c>
       <c r="J21" s="1">
-        <v>4938.609401579</v>
+        <v>115.627876555</v>
       </c>
       <c r="K21" s="1">
         <v>42.874690813</v>
@@ -1250,7 +1250,7 @@
         <v>124.846369995</v>
       </c>
       <c r="J22" s="1">
-        <v>4642.609092803</v>
+        <v>113.236032535</v>
       </c>
       <c r="K22" s="1">
         <v>46.782273951</v>
@@ -1288,7 +1288,7 @@
         <v>120.600542355</v>
       </c>
       <c r="J23" s="1">
-        <v>4684.039176902</v>
+        <v>114.012631624</v>
       </c>
       <c r="K23" s="1">
         <v>52.127268108</v>
@@ -1326,7 +1326,7 @@
         <v>117.157465317</v>
       </c>
       <c r="J24" s="1">
-        <v>5048.381176548</v>
+        <v>117.934913538</v>
       </c>
       <c r="K24" s="1">
         <v>56.878127649</v>
@@ -1364,7 +1364,7 @@
         <v>115.559999336</v>
       </c>
       <c r="J25" s="1">
-        <v>5667.88430012</v>
+        <v>124.111633188</v>
       </c>
       <c r="K25" s="1">
         <v>58.691735834</v>
@@ -1402,7 +1402,7 @@
         <v>116.338643783</v>
       </c>
       <c r="J26" s="1">
-        <v>6393.931052957</v>
+        <v>130.879196051</v>
       </c>
       <c r="K26" s="1">
         <v>56.48175031</v>
@@ -1440,7 +1440,7 @@
         <v>119.492726885</v>
       </c>
       <c r="J27" s="1">
-        <v>6982.605642324</v>
+        <v>136.129515137</v>
       </c>
       <c r="K27" s="1">
         <v>51.560074603</v>
@@ -1478,7 +1478,7 @@
         <v>124.514462829</v>
       </c>
       <c r="J28" s="1">
-        <v>7172.132411293</v>
+        <v>138.055170734</v>
       </c>
       <c r="K28" s="1">
         <v>46.663273853</v>
@@ -1516,7 +1516,7 @@
         <v>130.426962254</v>
       </c>
       <c r="J29" s="1">
-        <v>6855.742688035</v>
+        <v>136.07313714</v>
       </c>
       <c r="K29" s="1">
         <v>43.968884181</v>
@@ -1554,7 +1554,7 @@
         <v>135.90821439</v>
       </c>
       <c r="J30" s="1">
-        <v>6191.157630115</v>
+        <v>131.244350794</v>
       </c>
       <c r="K30" s="1">
         <v>44.334346339</v>
@@ -1592,7 +1592,7 @@
         <v>139.592852516</v>
       </c>
       <c r="J31" s="1">
-        <v>5491.720254991</v>
+        <v>125.74511282</v>
       </c>
       <c r="K31" s="1">
         <v>47.631260768</v>
@@ -1630,7 +1630,7 @@
         <v>140.533430571</v>
       </c>
       <c r="J32" s="1">
-        <v>5015.881128568</v>
+        <v>121.800491623</v>
       </c>
       <c r="K32" s="1">
         <v>52.946737827</v>
@@ -1668,7 +1668,7 @@
         <v>138.617228527</v>
       </c>
       <c r="J33" s="1">
-        <v>4879.916728151</v>
+        <v>120.880406814</v>
       </c>
       <c r="K33" s="1">
         <v>58.440550771</v>
@@ -1706,7 +1706,7 @@
         <v>134.659785324</v>
       </c>
       <c r="J34" s="1">
-        <v>5099.291148777</v>
+        <v>123.45159325</v>
       </c>
       <c r="K34" s="1">
         <v>61.612574699</v>
@@ -1744,7 +1744,7 @@
         <v>130.080218946</v>
       </c>
       <c r="J35" s="1">
-        <v>5632.138529856</v>
+        <v>129.017586361</v>
       </c>
       <c r="K35" s="1">
         <v>60.672231826</v>
@@ -1782,7 +1782,7 @@
         <v>126.36650252</v>
       </c>
       <c r="J36" s="1">
-        <v>6368.942555009</v>
+        <v>136.193186536</v>
       </c>
       <c r="K36" s="1">
         <v>56.151182808</v>
@@ -1820,7 +1820,7 @@
         <v>124.643469436</v>
       </c>
       <c r="J37" s="1">
-        <v>7100.009315193</v>
+        <v>142.894322236</v>
       </c>
       <c r="K37" s="1">
         <v>50.669205764</v>
@@ -1858,7 +1858,7 @@
         <v>125.483318396</v>
       </c>
       <c r="J38" s="1">
-        <v>7539.936672669</v>
+        <v>146.905835767</v>
       </c>
       <c r="K38" s="1">
         <v>46.89354174</v>
@@ -1896,7 +1896,7 @@
         <v>128.885324825</v>
       </c>
       <c r="J39" s="1">
-        <v>7469.853407413</v>
+        <v>146.842769799</v>
       </c>
       <c r="K39" s="1">
         <v>46.177843557</v>
@@ -1934,7 +1934,7 @@
         <v>134.30178895</v>
       </c>
       <c r="J40" s="1">
-        <v>6915.441254177</v>
+        <v>142.966223581</v>
       </c>
       <c r="K40" s="1">
         <v>48.684274841</v>
@@ -1972,7 +1972,7 @@
         <v>140.679034067</v>
       </c>
       <c r="J41" s="1">
-        <v>6153.009615113</v>
+        <v>137.131548377</v>
       </c>
       <c r="K41" s="1">
         <v>53.735809841</v>
@@ -2010,7 +2010,7 @@
         <v>146.591134161</v>
       </c>
       <c r="J42" s="1">
-        <v>5507.77140867</v>
+        <v>131.830384951</v>
       </c>
       <c r="K42" s="1">
         <v>59.732532579</v>
@@ -2048,7 +2048,7 @@
         <v>150.565399325</v>
       </c>
       <c r="J43" s="1">
-        <v>5177.657827079</v>
+        <v>129.103380639</v>
       </c>
       <c r="K43" s="1">
         <v>64.174529919</v>
@@ -2086,7 +2086,7 @@
         <v>151.579910511</v>
       </c>
       <c r="J44" s="1">
-        <v>5223.862621608</v>
+        <v>129.988801698</v>
       </c>
       <c r="K44" s="1">
         <v>64.707938092</v>
@@ -2124,7 +2124,7 @@
         <v>149.513087456</v>
       </c>
       <c r="J45" s="1">
-        <v>5630.19409783</v>
+        <v>134.460698528</v>
       </c>
       <c r="K45" s="1">
         <v>60.971629306</v>
@@ -2162,7 +2162,7 @@
         <v>145.244573664</v>
       </c>
       <c r="J46" s="1">
-        <v>6321.093359979</v>
+        <v>141.502939149</v>
       </c>
       <c r="K46" s="1">
         <v>55.180987566</v>
@@ -2200,7 +2200,7 @@
         <v>140.305035371</v>
       </c>
       <c r="J47" s="1">
-        <v>7130.81513011</v>
+        <v>149.218815666</v>
       </c>
       <c r="K47" s="1">
         <v>50.372657008</v>
@@ -2238,7 +2238,7 @@
         <v>136.29940624</v>
       </c>
       <c r="J48" s="1">
-        <v>7787.33294893</v>
+        <v>155.204842625</v>
       </c>
       <c r="K48" s="1">
         <v>48.475919057</v>
@@ -2276,7 +2276,7 @@
         <v>134.440935983</v>
       </c>
       <c r="J49" s="1">
-        <v>7998.702189625</v>
+        <v>157.400333247</v>
       </c>
       <c r="K49" s="1">
         <v>50.02161557</v>
@@ -2314,7 +2314,7 @@
         <v>135.346800372</v>
       </c>
       <c r="J50" s="1">
-        <v>7645.849366075</v>
+        <v>155.140564586</v>
       </c>
       <c r="K50" s="1">
         <v>54.580566733</v>
@@ -2352,7 +2352,7 @@
         <v>139.016217877</v>
       </c>
       <c r="J51" s="1">
-        <v>6904.672592819</v>
+        <v>149.635138198</v>
       </c>
       <c r="K51" s="1">
         <v>60.816535737</v>
@@ -2390,7 +2390,7 @@
         <v>144.858437368</v>
       </c>
       <c r="J52" s="1">
-        <v>6124.626862611</v>
+        <v>143.365312264</v>
       </c>
       <c r="K52" s="1">
         <v>66.35933185</v>
@@ -2428,7 +2428,7 @@
         <v>151.736959014</v>
       </c>
       <c r="J53" s="1">
-        <v>5593.948503071</v>
+        <v>138.867945831</v>
       </c>
       <c r="K53" s="1">
         <v>68.475256413</v>
@@ -2466,7 +2466,7 @@
         <v>158.113773411</v>
       </c>
       <c r="J54" s="1">
-        <v>5442.314555876</v>
+        <v>137.818932926</v>
       </c>
       <c r="K54" s="1">
         <v>65.896881055</v>
@@ -2504,7 +2504,7 @@
         <v>162.400431435</v>
       </c>
       <c r="J55" s="1">
-        <v>5686.971313167</v>
+        <v>140.750410246</v>
       </c>
       <c r="K55" s="1">
         <v>60.154794861</v>
@@ -2542,7 +2542,7 @@
         <v>163.494687187</v>
       </c>
       <c r="J56" s="1">
-        <v>6281.227981806</v>
+        <v>147.096345467</v>
       </c>
       <c r="K56" s="1">
         <v>54.441730114</v>
@@ -2580,7 +2580,7 @@
         <v>161.265403718</v>
       </c>
       <c r="J57" s="1">
-        <v>7102.946772167</v>
+        <v>155.277436062</v>
       </c>
       <c r="K57" s="1">
         <v>51.298203669</v>
@@ -2618,7 +2618,7 @@
         <v>156.661367966</v>
       </c>
       <c r="J58" s="1">
-        <v>7918.267092556</v>
+        <v>162.917577223</v>
       </c>
       <c r="K58" s="1">
         <v>51.724585929</v>
@@ -2656,7 +2656,7 @@
         <v>151.333562551</v>
       </c>
       <c r="J59" s="1">
-        <v>8408.89494432</v>
+        <v>167.491209368</v>
       </c>
       <c r="K59" s="1">
         <v>55.571073985</v>
@@ -2694,7 +2694,7 @@
         <v>147.013075228</v>
       </c>
       <c r="J60" s="1">
-        <v>8330.734763343</v>
+        <v>167.419306198</v>
       </c>
       <c r="K60" s="1">
         <v>61.772605588</v>
@@ -2732,7 +2732,7 @@
         <v>145.008521905</v>
       </c>
       <c r="J61" s="1">
-        <v>7712.428038127</v>
+        <v>162.999553838</v>
       </c>
       <c r="K61" s="1">
         <v>68.182200477</v>
@@ -2770,7 +2770,7 @@
         <v>145.985590795</v>
       </c>
       <c r="J62" s="1">
-        <v>6862.128117392</v>
+        <v>156.347287091</v>
       </c>
       <c r="K62" s="1">
         <v>71.882979619</v>
@@ -2808,7 +2808,7 @@
         <v>149.943438937</v>
       </c>
       <c r="J63" s="1">
-        <v>6142.527870389</v>
+        <v>150.303291162</v>
       </c>
       <c r="K63" s="1">
         <v>70.785887867</v>
@@ -2846,7 +2846,7 @@
         <v>156.24487984</v>
       </c>
       <c r="J64" s="1">
-        <v>5774.369549198</v>
+        <v>147.194161782</v>
       </c>
       <c r="K64" s="1">
         <v>65.511210156</v>
@@ -2884,7 +2884,7 @@
         <v>163.664080319</v>
       </c>
       <c r="J65" s="1">
-        <v>5825.899327231</v>
+        <v>148.203653632</v>
       </c>
       <c r="K65" s="1">
         <v>59.115424133</v>
@@ -2922,7 +2922,7 @@
         <v>170.542137389</v>
       </c>
       <c r="J66" s="1">
-        <v>6279.059459</v>
+        <v>153.302180892</v>
       </c>
       <c r="K66" s="1">
         <v>54.71038212</v>
@@ -2960,7 +2960,7 @@
         <v>175.165743581</v>
       </c>
       <c r="J67" s="1">
-        <v>7049.583080714</v>
+        <v>161.331224749</v>
       </c>
       <c r="K67" s="1">
         <v>53.875381827</v>
@@ -2998,7 +2998,7 @@
         <v>176.346012136</v>
       </c>
       <c r="J68" s="1">
-        <v>7952.623198257</v>
+        <v>170.128298618</v>
       </c>
       <c r="K68" s="1">
         <v>56.799618475</v>
@@ -3036,7 +3036,7 @@
         <v>173.941498224</v>
       </c>
       <c r="J69" s="1">
-        <v>8684.803003897</v>
+        <v>176.953125484</v>
       </c>
       <c r="K69" s="1">
         <v>62.693210639</v>
@@ -3074,7 +3074,7 @@
         <v>168.975567169</v>
       </c>
       <c r="J70" s="1">
-        <v>8920.5320049</v>
+        <v>179.456262119</v>
       </c>
       <c r="K70" s="1">
         <v>69.689547028</v>
@@ -3112,7 +3112,7 @@
         <v>163.228975309</v>
       </c>
       <c r="J71" s="1">
-        <v>8527.013802712</v>
+        <v>176.8798404</v>
       </c>
       <c r="K71" s="1">
         <v>74.871995673</v>
@@ -3150,7 +3150,7 @@
         <v>158.568880703</v>
       </c>
       <c r="J72" s="1">
-        <v>7700.418316297</v>
+        <v>170.602958893</v>
       </c>
       <c r="K72" s="1">
         <v>75.494319428</v>
@@ -3188,7 +3188,7 @@
         <v>156.406761612</v>
       </c>
       <c r="J73" s="1">
-        <v>6830.474325804</v>
+        <v>163.454565348</v>
       </c>
       <c r="K73" s="1">
         <v>71.135192908</v>
@@ -3226,7 +3226,7 @@
         <v>157.460631956</v>
       </c>
       <c r="J74" s="1">
-        <v>6238.636652848</v>
+        <v>158.326999523</v>
       </c>
       <c r="K74" s="1">
         <v>64.379289844</v>
@@ -3264,7 +3264,7 @@
         <v>161.729582516</v>
       </c>
       <c r="J75" s="1">
-        <v>6069.527283988</v>
+        <v>157.130992305</v>
       </c>
       <c r="K75" s="1">
         <v>58.769442679</v>
@@ -3302,7 +3302,7 @@
         <v>168.526341439</v>
       </c>
       <c r="J76" s="1">
-        <v>6342.380102094</v>
+        <v>160.473246743</v>
       </c>
       <c r="K76" s="1">
         <v>56.556531173</v>
@@ -3340,7 +3340,7 @@
         <v>176.528720234</v>
       </c>
       <c r="J77" s="1">
-        <v>7005.123320437</v>
+        <v>167.70841449</v>
       </c>
       <c r="K77" s="1">
         <v>58.359884977</v>
@@ -3378,7 +3378,7 @@
         <v>183.947419619</v>
       </c>
       <c r="J78" s="1">
-        <v>7921.543083877</v>
+        <v>177.035891173</v>
       </c>
       <c r="K78" s="1">
         <v>63.678782866</v>
@@ -3416,7 +3416,7 @@
         <v>188.934459429</v>
       </c>
       <c r="J79" s="1">
-        <v>8830.826970169</v>
+        <v>185.746617169</v>
       </c>
       <c r="K79" s="1">
         <v>70.954246276</v>
@@ -3454,7 +3454,7 @@
         <v>190.20750173</v>
       </c>
       <c r="J80" s="1">
-        <v>9377.998417536</v>
+        <v>190.961135538</v>
       </c>
       <c r="K80" s="1">
         <v>77.420989501</v>
@@ -3492,7 +3492,7 @@
         <v>187.613983576</v>
       </c>
       <c r="J81" s="1">
-        <v>9290.830477115</v>
+        <v>190.879156842</v>
       </c>
       <c r="K81" s="1">
         <v>79.889624564</v>
@@ -3530,7 +3530,7 @@
         <v>182.257710823</v>
       </c>
       <c r="J82" s="1">
-        <v>8601.265495149</v>
+        <v>185.840080866</v>
       </c>
       <c r="K82" s="1">
         <v>76.881451246</v>
@@ -3568,7 +3568,7 @@
         <v>176.059414259</v>
       </c>
       <c r="J83" s="1">
-        <v>7652.970699712</v>
+        <v>178.255656484</v>
       </c>
       <c r="K83" s="1">
         <v>70.182197614</v>
@@ -3606,7 +3606,7 @@
         <v>171.033017903</v>
       </c>
       <c r="J84" s="1">
-        <v>6850.438378599</v>
+        <v>171.364737671</v>
       </c>
       <c r="K84" s="1">
         <v>63.516803109</v>
@@ -3644,7 +3644,7 @@
         <v>168.700947754</v>
       </c>
       <c r="J85" s="1">
-        <v>6439.850759609</v>
+        <v>167.819937445</v>
       </c>
       <c r="K85" s="1">
         <v>59.84927179</v>
@@ -3682,7 +3682,7 @@
         <v>169.837656449</v>
       </c>
       <c r="J86" s="1">
-        <v>6497.319211771</v>
+        <v>168.970885669</v>
       </c>
       <c r="K86" s="1">
         <v>60.346729127</v>
@@ -3879,16 +3879,16 @@
         <v>Рублёвая масса М2</v>
       </c>
       <c r="B2" s="2">
-        <v>0.9066999786825691</v>
+        <v>0.9066999946982839</v>
       </c>
       <c r="C2" s="2">
-        <v>0.9999999999999996</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>0.5881016597724009</v>
+        <v>0.5937405019029445</v>
       </c>
       <c r="E2" s="2">
-        <v>0.9999999999999996</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
         <v>0.14281562857104302</v>
@@ -3905,16 +3905,16 @@
         <v>Золото</v>
       </c>
       <c r="B3" s="2">
-        <v>0.014928001252270126</v>
+        <v>0.01492800025852572</v>
       </c>
       <c r="C3" s="2">
-        <v>4.917285190495006e-16</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>0.03336921396655617</v>
+        <v>0.029286774305533572</v>
       </c>
       <c r="E3" s="2">
-        <v>4.917285190495006e-16</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
         <v>0.04947062857107497</v>
@@ -3931,13 +3931,13 @@
         <v>Доллар США</v>
       </c>
       <c r="B4" s="2">
-        <v>0.011196002913737266</v>
+        <v>0.011196000597908835</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>0.05482208610104843</v>
+        <v>0.04650821988216066</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
@@ -3957,13 +3957,13 @@
         <v>Евро</v>
       </c>
       <c r="B5" s="2">
-        <v>0.007464002670123036</v>
+        <v>0.0074640005494002</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>0.04748637638587217</v>
+        <v>0.040015686416352614</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -3983,13 +3983,13 @@
         <v>Юань</v>
       </c>
       <c r="B6" s="2">
-        <v>0.007464004216342095</v>
+        <v>0.0074640008657824415</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>0.07080480604183025</v>
+        <v>0.05922374449723081</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -4009,13 +4009,13 @@
         <v>Индекс Мосбиржи</v>
       </c>
       <c r="B7" s="2">
-        <v>0.012129001046601329</v>
+        <v>0.012129000217746221</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>0.02751678765051311</v>
+        <v>0.024128538680897742</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -4035,13 +4035,13 @@
         <v>ОФЗ / RGBITR</v>
       </c>
       <c r="B8" s="2">
-        <v>0.009330007268941847</v>
+        <v>0.009330001490414571</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>0.11869667323956543</v>
+        <v>0.09889859626726404</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -4058,25 +4058,25 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Нефть Brent</v>
+        <v>Индекс недвижимости</v>
       </c>
       <c r="B9" s="2">
-        <v>0.009330000438578689</v>
+        <v>0.0093300010086206</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>0.015621471122218891</v>
+        <v>0.0697121605393884</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>0.057960928570949935</v>
+        <v>0.03327374857134602</v>
       </c>
       <c r="G9" s="2">
-        <v>0.2999999999997348</v>
+        <v>0.119999999999737</v>
       </c>
       <c r="H9" s="2">
         <v>0.009330000000000005</v>
@@ -4087,13 +4087,13 @@
         <v>Серебро</v>
       </c>
       <c r="B10" s="2">
-        <v>0.009330000715982495</v>
+        <v>0.009330000145576804</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>0.019890858188340542</v>
+        <v>0.01750941774145029</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
@@ -4113,13 +4113,13 @@
         <v>Индекс S&amp;P 500</v>
       </c>
       <c r="B11" s="2">
-        <v>0.012129000794853973</v>
+        <v>0.012129000167740668</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>0.023690067531654067</v>
+        <v>0.020976359766777482</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -4156,16 +4156,16 @@
         <v>Ожидаемая реальная доходность</v>
       </c>
       <c r="B13" s="2">
-        <v>0.13370662646590545</v>
+        <v>0.13347629676407705</v>
       </c>
       <c r="C13" s="2">
-        <v>0.142815628571043</v>
+        <v>0.14281562857104302</v>
       </c>
       <c r="D13" s="2">
-        <v>0.1</v>
+        <v>0.10000000000000003</v>
       </c>
       <c r="E13" s="2">
-        <v>0.142815628571043</v>
+        <v>0.14281562857104302</v>
       </c>
     </row>
     <row r="14">
@@ -4173,16 +4173,16 @@
         <v>Ожидаемая волатильность</v>
       </c>
       <c r="B14" s="2">
-        <v>0.05480750617019898</v>
+        <v>0.05474743767693733</v>
       </c>
       <c r="C14" s="2">
-        <v>0.05999999999997697</v>
+        <v>0.059999999999977</v>
       </c>
       <c r="D14" s="2">
-        <v>0.04193202500564396</v>
+        <v>0.04116286926233839</v>
       </c>
       <c r="E14" s="2">
-        <v>0.05999999999997697</v>
+        <v>0.059999999999977</v>
       </c>
     </row>
     <row r="15">
@@ -4190,16 +4190,16 @@
         <v>Коэффициент Шарпа</v>
       </c>
       <c r="B15">
-        <v>1.9182627570826172</v>
+        <v>1.9161603290382268</v>
       </c>
       <c r="C15">
-        <v>1.9040700000008306</v>
+        <v>1.90407000000083</v>
       </c>
       <c r="D15">
-        <v>1.7034372038876935</v>
+        <v>1.7352670673595627</v>
       </c>
       <c r="E15">
-        <v>1.9040700000008306</v>
+        <v>1.90407000000083</v>
       </c>
     </row>
     <row r="16">
@@ -4340,10 +4340,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Нефть Brent</v>
+        <v>Индекс недвижимости</v>
       </c>
       <c r="B9" t="str">
-        <v>₽ за баррель, условный уровень</v>
+        <v>Индекс рублёвых цен на жильё, январь 2019 = 100; без арендного дохода</v>
       </c>
       <c r="C9" t="str">
         <v>Синтетический генератор</v>
